--- a/downloads/SD_Biosensor_half_year.xlsx
+++ b/downloads/SD_Biosensor_half_year.xlsx
@@ -504,7 +504,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Dashboard updated_at: 2026-10-08T08:00:34.836594+00:00</t>
+          <t>Dashboard updated_at: 2026-10-22T15:01:20.109515+00:00</t>
         </is>
       </c>
     </row>

--- a/downloads/SD_Biosensor_half_year.xlsx
+++ b/downloads/SD_Biosensor_half_year.xlsx
@@ -504,7 +504,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Dashboard updated_at: 2026-10-22T15:01:20.109515+00:00</t>
+          <t>Dashboard updated_at: 2026-10-22T17:00:25.440107+00:00</t>
         </is>
       </c>
     </row>

--- a/downloads/SD_Biosensor_half_year.xlsx
+++ b/downloads/SD_Biosensor_half_year.xlsx
@@ -504,7 +504,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Dashboard updated_at: 2026-10-22T17:00:25.440107+00:00</t>
+          <t>Dashboard updated_at: 2026-10-22T17:05:49.312133+00:00</t>
         </is>
       </c>
     </row>

--- a/downloads/SD_Biosensor_half_year.xlsx
+++ b/downloads/SD_Biosensor_half_year.xlsx
@@ -504,7 +504,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Dashboard updated_at: 2026-10-22T17:05:49.312133+00:00</t>
+          <t>Dashboard updated_at: 2026-10-27T15:00:14.491938+00:00</t>
         </is>
       </c>
     </row>

--- a/downloads/SD_Biosensor_half_year.xlsx
+++ b/downloads/SD_Biosensor_half_year.xlsx
@@ -504,7 +504,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Dashboard updated_at: 2026-10-27T15:00:14.491938+00:00</t>
+          <t>Dashboard updated_at: 2026-10-27T15:02:51.318929+00:00</t>
         </is>
       </c>
     </row>
